--- a/artfynd/A 55331-2024 artfynd.xlsx
+++ b/artfynd/A 55331-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111057153</v>
+        <v>111057152</v>
       </c>
       <c r="B2" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,21 +703,21 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fagerdal, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639981.1858983048</v>
+        <v>639908</v>
       </c>
       <c r="R2" t="n">
-        <v>6701636.17355721</v>
+        <v>6701744</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,27 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Överflygande</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +769,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elsa Fogelström</t>
+          <t>Liam Martin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111057152</v>
+        <v>111057153</v>
       </c>
       <c r="B3" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,21 +804,21 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fagerdal, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639907.7099456429</v>
+        <v>639981</v>
       </c>
       <c r="R3" t="n">
-        <v>6701744.050819736</v>
+        <v>6701636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +845,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Överflygande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +875,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Martin</t>
+          <t>Elsa Fogelström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 55331-2024 artfynd.xlsx
+++ b/artfynd/A 55331-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111057152</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,8 +889,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111057153</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>